--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_VALENCIA BASKET.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_VALENCIA BASKET.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA50"/>
+  <dimension ref="A1:BA48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -671,13 +671,13 @@
         <v>0.2046941131204309</v>
       </c>
       <c r="J2" t="n">
-        <v>378</v>
+        <v>13</v>
       </c>
       <c r="K2" t="n">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="L2" t="n">
-        <v>448</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
         <v>441</v>
@@ -752,13 +752,13 @@
         <v>1.100826446280992</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.75</v>
+        <v>0.02579365079365079</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.01419878296146</v>
+        <v>0.0385395537525355</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.828571428571429</v>
+        <v>2.5</v>
       </c>
       <c r="AN2" t="n">
         <v>1.664583333333333</v>
@@ -801,13 +801,13 @@
         <v>0.204694113120431</v>
       </c>
       <c r="J3" t="n">
-        <v>9.947368421052632</v>
+        <v>0.3421052631578947</v>
       </c>
       <c r="K3" t="n">
-        <v>13.1578947368421</v>
+        <v>0.5</v>
       </c>
       <c r="L3" t="n">
-        <v>11.78947368421053</v>
+        <v>0.131578947368421</v>
       </c>
       <c r="M3" t="n">
         <v>11.60526315789474</v>
@@ -882,13 +882,13 @@
         <v>1.100826446280992</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.75</v>
+        <v>0.02579365079365079</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.01419878296146</v>
+        <v>0.0385395537525355</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.828571428571428</v>
+        <v>2.5</v>
       </c>
       <c r="AN3" t="n">
         <v>1.664583333333333</v>
@@ -931,13 +931,13 @@
         <v>0.2434607645875252</v>
       </c>
       <c r="J4" t="n">
-        <v>318</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>423</v>
+        <v>9</v>
       </c>
       <c r="L4" t="n">
-        <v>343</v>
+        <v>14</v>
       </c>
       <c r="M4" t="n">
         <v>450</v>
@@ -1012,13 +1012,13 @@
         <v>1.042348411934553</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.6625</v>
+        <v>0.01041666666666667</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.014388489208633</v>
+        <v>0.02158273381294964</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.625592417061611</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="AN4" t="n">
         <v>1.462301587301587</v>
@@ -1061,13 +1061,13 @@
         <v>0.2434607645875252</v>
       </c>
       <c r="J5" t="n">
-        <v>8.368421052631579</v>
+        <v>0.131578947368421</v>
       </c>
       <c r="K5" t="n">
-        <v>11.13157894736842</v>
+        <v>0.2368421052631579</v>
       </c>
       <c r="L5" t="n">
-        <v>9.026315789473685</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="M5" t="n">
         <v>11.8421052631579</v>
@@ -1142,13 +1142,13 @@
         <v>1.042348411934552</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.6625</v>
+        <v>0.01041666666666667</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.014388489208633</v>
+        <v>0.02158273381294964</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.625592417061612</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="AN5" t="n">
         <v>1.462301587301587</v>
@@ -1486,16 +1486,16 @@
         <v>323</v>
       </c>
       <c r="U8" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="V8" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="W8" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="X8" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
         <v>92</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>1312:42</t>
+          <t>647:54</t>
         </is>
       </c>
       <c r="AO8" t="n">
@@ -1575,13 +1575,13 @@
         <v>6.889</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.13</v>
+        <v>0.264</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.017</v>
+        <v>0.035</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.046</v>
+        <v>0.094</v>
       </c>
       <c r="BA8" t="n">
         <v>0.063</v>
@@ -1651,16 +1651,16 @@
         <v>490</v>
       </c>
       <c r="U9" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>128</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>1692:31</t>
+          <t>795:08</t>
         </is>
       </c>
       <c r="AO9" t="n">
@@ -1740,13 +1740,13 @@
         <v>7.34</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.096</v>
+        <v>0.204</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.02</v>
+        <v>0.042</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.075</v>
+        <v>0.16</v>
       </c>
       <c r="BA9" t="n">
         <v>0.06</v>
@@ -1816,16 +1816,16 @@
         <v>200</v>
       </c>
       <c r="U10" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="V10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
         <v>38</v>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>1055:08</t>
+          <t>563:58</t>
         </is>
       </c>
       <c r="AO10" t="n">
@@ -1905,13 +1905,13 @@
         <v>11.067</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.135</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.026</v>
+        <v>0.048</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.068</v>
+        <v>0.128</v>
       </c>
       <c r="BA10" t="n">
         <v>0.02</v>
@@ -1981,16 +1981,16 @@
         <v>458</v>
       </c>
       <c r="U11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="W11" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>145</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>1405:32</t>
+          <t>720:30</t>
         </is>
       </c>
       <c r="AO11" t="n">
@@ -2070,13 +2070,13 @@
         <v>9.741</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.101</v>
+        <v>0.198</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.036</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.068</v>
+        <v>0.133</v>
       </c>
       <c r="BA11" t="n">
         <v>0.015</v>
@@ -2146,16 +2146,16 @@
         <v>382</v>
       </c>
       <c r="U12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>82</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>1763:06</t>
+          <t>779:37</t>
         </is>
       </c>
       <c r="AO12" t="n">
@@ -2235,13 +2235,13 @@
         <v>5.327</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.067</v>
+        <v>0.152</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.031</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.067</v>
+        <v>0.152</v>
       </c>
       <c r="BA12" t="n">
         <v>0.067</v>
@@ -2311,16 +2311,16 @@
         <v>109</v>
       </c>
       <c r="U13" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>30</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>640:04</t>
+          <t>279:14</t>
         </is>
       </c>
       <c r="AO13" t="n">
@@ -2400,13 +2400,13 @@
         <v>4.061</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.198</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.02</v>
+        <v>0.047</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.039</v>
+        <v>0.089</v>
       </c>
       <c r="BA13" t="n">
         <v>0.047</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>114:49</t>
+          <t>84:44</t>
         </is>
       </c>
       <c r="AO14" t="n">
@@ -2565,13 +2565,13 @@
         <v>4.667</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.114</v>
+        <v>0.155</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.019</v>
+        <v>0.026</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.093</v>
       </c>
       <c r="BA14" t="n">
         <v>0.006</v>
@@ -2641,16 +2641,16 @@
         <v>172</v>
       </c>
       <c r="U15" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>65</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>729:22</t>
+          <t>452:30</t>
         </is>
       </c>
       <c r="AO15" t="n">
@@ -2730,13 +2730,13 @@
         <v>5.241</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.109</v>
+        <v>0.176</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.04</v>
+        <v>0.065</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.102</v>
+        <v>0.165</v>
       </c>
       <c r="BA15" t="n">
         <v>0.023</v>
@@ -2806,16 +2806,16 @@
         <v>551</v>
       </c>
       <c r="U16" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="V16" t="n">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="W16" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>151</v>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>1419:06</t>
+          <t>700:50</t>
         </is>
       </c>
       <c r="AO16" t="n">
@@ -2895,13 +2895,13 @@
         <v>12.225</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.138</v>
+        <v>0.28</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.019</v>
+        <v>0.039</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.052</v>
+        <v>0.106</v>
       </c>
       <c r="BA16" t="n">
         <v>0.132</v>
@@ -2971,16 +2971,16 @@
         <v>367</v>
       </c>
       <c r="U17" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="W17" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>117</v>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>1447:52</t>
+          <t>712:08</t>
         </is>
       </c>
       <c r="AO17" t="n">
@@ -3060,13 +3060,13 @@
         <v>6.534</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.109</v>
+        <v>0.222</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.023</v>
+        <v>0.047</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.045</v>
+        <v>0.092</v>
       </c>
       <c r="BA17" t="n">
         <v>0.104</v>
@@ -3136,16 +3136,16 @@
         <v>263</v>
       </c>
       <c r="U18" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="W18" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>93</v>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>868:17</t>
+          <t>475:46</t>
         </is>
       </c>
       <c r="AO18" t="n">
@@ -3225,13 +3225,13 @@
         <v>4.867</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.094</v>
+        <v>0.172</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.079</v>
+        <v>0.144</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.092</v>
+        <v>0.168</v>
       </c>
       <c r="BA18" t="n">
         <v>0.019</v>
@@ -3301,16 +3301,16 @@
         <v>417</v>
       </c>
       <c r="U19" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>77</v>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>1457:10</t>
+          <t>725:41</t>
         </is>
       </c>
       <c r="AO19" t="n">
@@ -3390,13 +3390,13 @@
         <v>10.25</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.105</v>
+        <v>0.21</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.025</v>
+        <v>0.051</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.033</v>
+        <v>0.067</v>
       </c>
       <c r="BA19" t="n">
         <v>0.117</v>
@@ -3469,13 +3469,13 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
         <v>4</v>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>35:26</t>
+          <t>24:41</t>
         </is>
       </c>
       <c r="AO20" t="n">
@@ -3555,7 +3555,7 @@
         <v>2.333</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.137</v>
+        <v>0.196</v>
       </c>
       <c r="AY20" t="n">
         <v>0</v>
@@ -3631,16 +3631,16 @@
         <v>274</v>
       </c>
       <c r="U21" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
         <v>56</v>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>1170:53</t>
+          <t>566:58</t>
         </is>
       </c>
       <c r="AO21" t="n">
@@ -3720,13 +3720,13 @@
         <v>8.173999999999999</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.078</v>
+        <v>0.161</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.032</v>
+        <v>0.065</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.094</v>
+        <v>0.195</v>
       </c>
       <c r="BA21" t="n">
         <v>0.027</v>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>92:19</t>
+          <t>42:18</t>
         </is>
       </c>
       <c r="AO22" t="n">
@@ -3885,13 +3885,13 @@
         <v>5</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.029</v>
+        <v>0.064</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.024</v>
+        <v>0.051</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.187</v>
       </c>
       <c r="BA22" t="n">
         <v>0.005</v>
@@ -3964,7 +3964,7 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>99:32</t>
+          <t>49:27</t>
         </is>
       </c>
       <c r="AO23" t="n">
@@ -4050,13 +4050,13 @@
         <v>4</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.102</v>
+        <v>0.205</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.066</v>
+        <v>0.132</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.034</v>
+        <v>0.068</v>
       </c>
       <c r="BA23" t="n">
         <v>0.001</v>
@@ -4129,7 +4129,7 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>69:56</t>
+          <t>28:56</t>
         </is>
       </c>
       <c r="AO24" t="n">
@@ -4215,13 +4215,13 @@
         <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.202</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.031</v>
+        <v>0.075</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.081</v>
+        <v>0.195</v>
       </c>
       <c r="BA24" t="n">
         <v>0.002</v>
@@ -4395,163 +4395,163 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>38</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>3454</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>795</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1389</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>444</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1210</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>532</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>738</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>799</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>939</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>493</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>441</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>717</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>778</v>
       </c>
       <c r="T26" t="n">
-        <v>136</v>
+        <v>4174</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1092</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1348</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>482</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>0.409</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>0.418</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>0.385</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>379</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1041</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>0.364</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>7650:00</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>17</v>
+        <v>3403.72</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>0.591</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.015</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>0.141</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>0.205</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>1.665</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>5.415</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>7.079</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="BA26" t="n">
         <v>0</v>
@@ -4560,44 +4560,44 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>38</v>
       </c>
       <c r="C27" t="n">
-        <v>3454</v>
+        <v>3280</v>
       </c>
       <c r="D27" t="n">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="E27" t="n">
-        <v>1389</v>
+        <v>1446</v>
       </c>
       <c r="F27" t="n">
-        <v>444</v>
+        <v>361</v>
       </c>
       <c r="G27" t="n">
-        <v>1210</v>
+        <v>1039</v>
       </c>
       <c r="H27" t="n">
-        <v>532</v>
+        <v>605</v>
       </c>
       <c r="I27" t="n">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="J27" t="n">
-        <v>799</v>
+        <v>737</v>
       </c>
       <c r="K27" t="n">
-        <v>939</v>
+        <v>912</v>
       </c>
       <c r="L27" t="n">
-        <v>493</v>
+        <v>417</v>
       </c>
       <c r="M27" t="n">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="N27" t="n">
         <v>211</v>
@@ -4606,76 +4606,76 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="Q27" t="n">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="R27" t="n">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="S27" t="n">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="T27" t="n">
-        <v>4174</v>
+        <v>3922</v>
       </c>
       <c r="U27" t="n">
-        <v>378</v>
+        <v>5</v>
       </c>
       <c r="V27" t="n">
-        <v>500</v>
+        <v>9</v>
       </c>
       <c r="W27" t="n">
-        <v>448</v>
+        <v>14</v>
       </c>
       <c r="X27" t="n">
-        <v>245</v>
+        <v>6</v>
       </c>
       <c r="Y27" t="n">
-        <v>1092</v>
+        <v>1128</v>
       </c>
       <c r="Z27" t="n">
-        <v>1348</v>
+        <v>1410</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>197</v>
+        <v>231</v>
       </c>
       <c r="AC27" t="n">
-        <v>482</v>
+        <v>550</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.409</v>
+        <v>0.42</v>
       </c>
       <c r="AE27" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AF27" t="n">
         <v>91</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.418</v>
+        <v>0.462</v>
       </c>
       <c r="AH27" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="AI27" t="n">
-        <v>169</v>
+        <v>130</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.385</v>
+        <v>0.377</v>
       </c>
       <c r="AK27" t="n">
-        <v>379</v>
+        <v>312</v>
       </c>
       <c r="AL27" t="n">
-        <v>1041</v>
+        <v>909</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.364</v>
+        <v>0.343</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
@@ -4683,40 +4683,40 @@
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>3403.72</v>
+        <v>3316.36</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.538</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.591</v>
+        <v>0.583</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.015</v>
+        <v>0.989</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.141</v>
+        <v>0.152</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.205</v>
+        <v>0.243</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.665</v>
+        <v>1.462</v>
       </c>
       <c r="AV27" t="n">
-        <v>5.415</v>
+        <v>4.931</v>
       </c>
       <c r="AW27" t="n">
-        <v>7.079</v>
+        <v>6.393</v>
       </c>
       <c r="AX27" t="n">
         <v>0.2</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.062</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.138</v>
+        <v>0.13</v>
       </c>
       <c r="BA27" t="n">
         <v>0</v>
@@ -4725,1047 +4725,1047 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>38</v>
-      </c>
-      <c r="C28" t="n">
-        <v>3280</v>
-      </c>
-      <c r="D28" t="n">
-        <v>796</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1446</v>
-      </c>
-      <c r="F28" t="n">
-        <v>361</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1039</v>
-      </c>
-      <c r="H28" t="n">
-        <v>605</v>
-      </c>
-      <c r="I28" t="n">
-        <v>744</v>
-      </c>
-      <c r="J28" t="n">
-        <v>737</v>
-      </c>
-      <c r="K28" t="n">
-        <v>912</v>
-      </c>
-      <c r="L28" t="n">
-        <v>417</v>
-      </c>
-      <c r="M28" t="n">
-        <v>254</v>
-      </c>
-      <c r="N28" t="n">
-        <v>211</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>504</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>450</v>
-      </c>
-      <c r="R28" t="n">
-        <v>703</v>
-      </c>
-      <c r="S28" t="n">
-        <v>785</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3922</v>
-      </c>
-      <c r="U28" t="n">
-        <v>318</v>
-      </c>
-      <c r="V28" t="n">
-        <v>423</v>
-      </c>
-      <c r="W28" t="n">
-        <v>343</v>
-      </c>
-      <c r="X28" t="n">
-        <v>211</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1128</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1410</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>231</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>550</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>91</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>49</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0.377</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>312</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>909</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>0.343</v>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>7650:00</t>
-        </is>
-      </c>
-      <c r="AO28" t="n">
-        <v>3316.36</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0.989</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0.152</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0.243</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>1.462</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>4.931</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>6.393</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr"/>
+      <c r="AX28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr"/>
+      <c r="BA28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="inlineStr"/>
-      <c r="AJ29" t="inlineStr"/>
-      <c r="AK29" t="inlineStr"/>
-      <c r="AL29" t="inlineStr"/>
-      <c r="AM29" t="inlineStr"/>
-      <c r="AN29" t="inlineStr"/>
-      <c r="AO29" t="inlineStr"/>
-      <c r="AP29" t="inlineStr"/>
-      <c r="AQ29" t="inlineStr"/>
-      <c r="AR29" t="inlineStr"/>
-      <c r="AS29" t="inlineStr"/>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AU29" t="inlineStr"/>
-      <c r="AV29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr"/>
-      <c r="AX29" t="inlineStr"/>
-      <c r="AY29" t="inlineStr"/>
-      <c r="AZ29" t="inlineStr"/>
-      <c r="BA29" t="inlineStr"/>
+          <t>#0 B. BADIO (Per Game)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>34</v>
+      </c>
+      <c r="C29" t="n">
+        <v>11.059</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2.029</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3.706</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.853</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5.176</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.441</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.676</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.059</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.588</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.588</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.029</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.059</v>
+      </c>
+      <c r="T29" t="n">
+        <v>323</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.706</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.235</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.324</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.441</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>4.471</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="AO29" t="n">
+        <v>11.208</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1.296</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>5.593</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>6.889</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0.07199999999999999</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>#0 B. BADIO (Per Game)</t>
+          <t>#1 K. TAYLOR (Per Game)</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>34</v>
       </c>
       <c r="C30" t="n">
-        <v>11.059</v>
+        <v>11.824</v>
       </c>
       <c r="D30" t="n">
-        <v>2.029</v>
+        <v>2.647</v>
       </c>
       <c r="E30" t="n">
-        <v>3.706</v>
+        <v>4.382</v>
       </c>
       <c r="F30" t="n">
-        <v>1.853</v>
+        <v>1.529</v>
       </c>
       <c r="G30" t="n">
-        <v>5.176</v>
+        <v>3.824</v>
       </c>
       <c r="H30" t="n">
-        <v>1.441</v>
+        <v>1.941</v>
       </c>
       <c r="I30" t="n">
-        <v>1.676</v>
+        <v>2.324</v>
       </c>
       <c r="J30" t="n">
-        <v>2.059</v>
+        <v>1.941</v>
       </c>
       <c r="K30" t="n">
+        <v>3.324</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.382</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.294</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.647</v>
+      </c>
+      <c r="T30" t="n">
+        <v>490</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>3.765</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>4.265</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="AC30" t="n">
         <v>1.588</v>
       </c>
-      <c r="L30" t="n">
+      <c r="AD30" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="AI30" t="n">
         <v>0.618</v>
       </c>
-      <c r="M30" t="n">
-        <v>0.588</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0.382</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.588</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R30" t="n">
-        <v>2.029</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.059</v>
-      </c>
-      <c r="T30" t="n">
-        <v>323</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0.618</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.412</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>2.706</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>3.235</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0.836</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0.5590000000000001</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.324</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0.422</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0.206</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0.588</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0.412</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0.706</v>
-      </c>
       <c r="AJ30" t="n">
-        <v>0.583</v>
+        <v>0.429</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.441</v>
+        <v>1.265</v>
       </c>
       <c r="AL30" t="n">
-        <v>4.471</v>
+        <v>3.206</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.322</v>
+        <v>0.394</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>38:36</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>11.208</v>
+        <v>10.611</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.541</v>
+        <v>0.602</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.575</v>
+        <v>0.641</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.987</v>
+        <v>1.114</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.142</v>
+        <v>0.13</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.162</v>
+        <v>0.237</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.296</v>
+        <v>1.404</v>
       </c>
       <c r="AV30" t="n">
-        <v>5.593</v>
+        <v>5.936</v>
       </c>
       <c r="AW30" t="n">
-        <v>6.889</v>
+        <v>7.34</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.13</v>
+        <v>0.204</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.017</v>
+        <v>0.042</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.046</v>
+        <v>0.16</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>#1 K. TAYLOR (Per Game)</t>
+          <t>#2 J. PUERTO (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C31" t="n">
-        <v>11.824</v>
+        <v>5.314</v>
       </c>
       <c r="D31" t="n">
-        <v>2.647</v>
+        <v>0.8</v>
       </c>
       <c r="E31" t="n">
-        <v>4.382</v>
+        <v>1.514</v>
       </c>
       <c r="F31" t="n">
-        <v>1.529</v>
+        <v>1.057</v>
       </c>
       <c r="G31" t="n">
-        <v>3.824</v>
+        <v>2.571</v>
       </c>
       <c r="H31" t="n">
-        <v>1.941</v>
+        <v>0.543</v>
       </c>
       <c r="I31" t="n">
-        <v>2.324</v>
+        <v>0.743</v>
       </c>
       <c r="J31" t="n">
-        <v>1.941</v>
+        <v>0.657</v>
       </c>
       <c r="K31" t="n">
-        <v>3.324</v>
+        <v>1.829</v>
       </c>
       <c r="L31" t="n">
-        <v>0.912</v>
+        <v>0.714</v>
       </c>
       <c r="M31" t="n">
-        <v>0.882</v>
+        <v>0.371</v>
       </c>
       <c r="N31" t="n">
-        <v>0.676</v>
+        <v>0.143</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.382</v>
+        <v>0.429</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.294</v>
+        <v>0.4</v>
       </c>
       <c r="R31" t="n">
-        <v>2</v>
+        <v>1.229</v>
       </c>
       <c r="S31" t="n">
-        <v>2.647</v>
+        <v>0.771</v>
       </c>
       <c r="T31" t="n">
-        <v>490</v>
+        <v>200</v>
       </c>
       <c r="U31" t="n">
-        <v>2</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="V31" t="n">
-        <v>1.824</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.853</v>
+        <v>0.057</v>
       </c>
       <c r="X31" t="n">
-        <v>0.882</v>
+        <v>0.029</v>
       </c>
       <c r="Y31" t="n">
-        <v>3.765</v>
+        <v>1.086</v>
       </c>
       <c r="Z31" t="n">
-        <v>4.265</v>
+        <v>1.314</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.883</v>
+        <v>0.826</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.588</v>
+        <v>0.143</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.588</v>
+        <v>0.429</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.37</v>
+        <v>0.333</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.235</v>
+        <v>0.114</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.471</v>
+        <v>0.314</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.5</v>
+        <v>0.364</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.265</v>
+        <v>0.314</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.618</v>
+        <v>0.657</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.429</v>
+        <v>0.478</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.265</v>
+        <v>0.743</v>
       </c>
       <c r="AL31" t="n">
-        <v>3.206</v>
+        <v>1.914</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.394</v>
+        <v>0.388</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>49:46</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>10.611</v>
+        <v>4.841</v>
       </c>
       <c r="AP31" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="AQ31" t="n">
         <v>0.602</v>
       </c>
-      <c r="AQ31" t="n">
-        <v>0.641</v>
-      </c>
       <c r="AR31" t="n">
-        <v>1.114</v>
+        <v>1.098</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.13</v>
+        <v>0.089</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.237</v>
+        <v>0.133</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.404</v>
+        <v>1.533</v>
       </c>
       <c r="AV31" t="n">
-        <v>5.936</v>
+        <v>9.532999999999999</v>
       </c>
       <c r="AW31" t="n">
-        <v>7.34</v>
+        <v>11.067</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.096</v>
+        <v>0.135</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.02</v>
+        <v>0.048</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0.075</v>
+        <v>0.128</v>
       </c>
       <c r="BA31" t="n">
-        <v>0.068</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#2 J. PUERTO (Per Game)</t>
+          <t>#3 N. REUVERS (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C32" t="n">
-        <v>5.314</v>
+        <v>10.789</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8</v>
+        <v>2.711</v>
       </c>
       <c r="E32" t="n">
-        <v>1.514</v>
+        <v>3.684</v>
       </c>
       <c r="F32" t="n">
-        <v>1.057</v>
+        <v>1.237</v>
       </c>
       <c r="G32" t="n">
-        <v>2.571</v>
+        <v>2.816</v>
       </c>
       <c r="H32" t="n">
-        <v>0.543</v>
+        <v>1.658</v>
       </c>
       <c r="I32" t="n">
-        <v>0.743</v>
+        <v>2.579</v>
       </c>
       <c r="J32" t="n">
-        <v>0.657</v>
+        <v>0.421</v>
       </c>
       <c r="K32" t="n">
-        <v>1.829</v>
+        <v>2.237</v>
       </c>
       <c r="L32" t="n">
-        <v>0.714</v>
+        <v>1.211</v>
       </c>
       <c r="M32" t="n">
-        <v>0.371</v>
+        <v>0.526</v>
       </c>
       <c r="N32" t="n">
-        <v>0.143</v>
+        <v>0.842</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.429</v>
+        <v>0.711</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.4</v>
+        <v>0.711</v>
       </c>
       <c r="R32" t="n">
-        <v>1.229</v>
+        <v>2.184</v>
       </c>
       <c r="S32" t="n">
-        <v>0.771</v>
+        <v>2.395</v>
       </c>
       <c r="T32" t="n">
-        <v>200</v>
+        <v>458</v>
       </c>
       <c r="U32" t="n">
-        <v>0.486</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>0.371</v>
+        <v>0.132</v>
       </c>
       <c r="W32" t="n">
-        <v>0.714</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0.371</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.086</v>
+        <v>3.816</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.314</v>
+        <v>4.342</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.826</v>
+        <v>0.879</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.143</v>
+        <v>0.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.429</v>
+        <v>0.895</v>
       </c>
       <c r="AD32" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="AJ32" t="n">
         <v>0.333</v>
       </c>
-      <c r="AE32" t="n">
-        <v>0.114</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0.657</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0.478</v>
-      </c>
       <c r="AK32" t="n">
-        <v>0.743</v>
+        <v>1.158</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.914</v>
+        <v>2.579</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.388</v>
+        <v>0.449</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>30:08</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>4.841</v>
+        <v>8.345000000000001</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.584</v>
+        <v>0.702</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.602</v>
+        <v>0.707</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.098</v>
+        <v>1.293</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.089</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AT32" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>9.148</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>9.741</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AZ32" t="n">
         <v>0.133</v>
       </c>
-      <c r="AU32" t="n">
-        <v>1.533</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>9.532999999999999</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>11.067</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>0.068</v>
-      </c>
       <c r="BA32" t="n">
-        <v>0.021</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#3 N. REUVERS (Per Game)</t>
+          <t>#4 J. PRADILLA (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>38</v>
       </c>
       <c r="C33" t="n">
-        <v>10.789</v>
+        <v>6.842</v>
       </c>
       <c r="D33" t="n">
-        <v>2.711</v>
+        <v>2.184</v>
       </c>
       <c r="E33" t="n">
-        <v>3.684</v>
+        <v>3.368</v>
       </c>
       <c r="F33" t="n">
-        <v>1.237</v>
+        <v>0.658</v>
       </c>
       <c r="G33" t="n">
-        <v>2.816</v>
+        <v>1.921</v>
       </c>
       <c r="H33" t="n">
-        <v>1.658</v>
+        <v>0.5</v>
       </c>
       <c r="I33" t="n">
-        <v>2.579</v>
+        <v>0.658</v>
       </c>
       <c r="J33" t="n">
-        <v>0.421</v>
+        <v>2</v>
       </c>
       <c r="K33" t="n">
-        <v>2.237</v>
+        <v>2.763</v>
       </c>
       <c r="L33" t="n">
-        <v>1.211</v>
+        <v>1.342</v>
       </c>
       <c r="M33" t="n">
-        <v>0.526</v>
+        <v>0.632</v>
       </c>
       <c r="N33" t="n">
-        <v>0.842</v>
+        <v>0.395</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.711</v>
+        <v>1.368</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.711</v>
+        <v>1.368</v>
       </c>
       <c r="R33" t="n">
-        <v>2.184</v>
+        <v>1.342</v>
       </c>
       <c r="S33" t="n">
-        <v>2.395</v>
+        <v>1.395</v>
       </c>
       <c r="T33" t="n">
-        <v>458</v>
+        <v>382</v>
       </c>
       <c r="U33" t="n">
-        <v>0.789</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.289</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.263</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0.789</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>3.816</v>
+        <v>2.158</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.342</v>
+        <v>2.737</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.879</v>
+        <v>0.788</v>
       </c>
       <c r="AB33" t="n">
         <v>0.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.895</v>
+        <v>1.105</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.452</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.053</v>
+        <v>0.026</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.105</v>
+        <v>0.026</v>
       </c>
       <c r="AG33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AK33" t="n">
         <v>0.5</v>
       </c>
-      <c r="AH33" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0.237</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1.158</v>
-      </c>
       <c r="AL33" t="n">
-        <v>2.579</v>
+        <v>1.289</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.449</v>
+        <v>0.388</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>36:59</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>8.345000000000001</v>
+        <v>6.947</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.702</v>
+        <v>0.6</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.707</v>
+        <v>0.613</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.293</v>
+        <v>0.985</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.197</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.255</v>
+        <v>0.095</v>
       </c>
       <c r="AU33" t="n">
-        <v>0.593</v>
+        <v>1.462</v>
       </c>
       <c r="AV33" t="n">
-        <v>9.148</v>
+        <v>3.865</v>
       </c>
       <c r="AW33" t="n">
-        <v>9.741</v>
+        <v>5.327</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.101</v>
+        <v>0.152</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.036</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.068</v>
+        <v>0.152</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.015</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#4 J. PRADILLA (Per Game)</t>
+          <t>#5 S. DE LARREA (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C34" t="n">
-        <v>6.842</v>
+        <v>3.481</v>
       </c>
       <c r="D34" t="n">
-        <v>2.184</v>
+        <v>0.704</v>
       </c>
       <c r="E34" t="n">
-        <v>3.368</v>
+        <v>1.556</v>
       </c>
       <c r="F34" t="n">
-        <v>0.658</v>
+        <v>0.444</v>
       </c>
       <c r="G34" t="n">
-        <v>1.921</v>
+        <v>1.296</v>
       </c>
       <c r="H34" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.074</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.111</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.222</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.222</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1.222</v>
+      </c>
+      <c r="T34" t="n">
+        <v>109</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="AG34" t="n">
         <v>0.5</v>
       </c>
-      <c r="I34" t="n">
-        <v>0.658</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2</v>
-      </c>
-      <c r="K34" t="n">
-        <v>2.763</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1.342</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.632</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1.368</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1.368</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.342</v>
-      </c>
-      <c r="S34" t="n">
-        <v>1.395</v>
-      </c>
-      <c r="T34" t="n">
-        <v>382</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0.658</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.079</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0.658</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0.368</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>2.158</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.737</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0.788</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.105</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0.452</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1</v>
-      </c>
       <c r="AH34" t="n">
-        <v>0.158</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.632</v>
+        <v>0.222</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.5</v>
+        <v>0.444</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.289</v>
+        <v>1.074</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.388</v>
+        <v>0.414</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>46:23</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>6.947</v>
+        <v>4.547</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.6</v>
+        <v>0.481</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.613</v>
+        <v>0.524</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.985</v>
+        <v>0.766</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.197</v>
+        <v>0.269</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.095</v>
+        <v>0.26</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.462</v>
+        <v>1.727</v>
       </c>
       <c r="AV34" t="n">
-        <v>3.865</v>
+        <v>2.333</v>
       </c>
       <c r="AW34" t="n">
-        <v>5.327</v>
+        <v>4.061</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.067</v>
+        <v>0.198</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.031</v>
+        <v>0.047</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.067</v>
+        <v>0.089</v>
       </c>
       <c r="BA34" t="n">
         <v>0.067</v>
@@ -5774,1743 +5774,1743 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#5 S. DE LARREA (Per Game)</t>
+          <t>#6 X. LOPEZ-AROSTEGUI (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C35" t="n">
-        <v>3.481</v>
+        <v>1.417</v>
       </c>
       <c r="D35" t="n">
-        <v>0.704</v>
+        <v>0.167</v>
       </c>
       <c r="E35" t="n">
-        <v>1.556</v>
+        <v>0.583</v>
       </c>
       <c r="F35" t="n">
-        <v>0.444</v>
+        <v>0.25</v>
       </c>
       <c r="G35" t="n">
-        <v>1.296</v>
+        <v>1.167</v>
       </c>
       <c r="H35" t="n">
-        <v>0.741</v>
+        <v>0.333</v>
       </c>
       <c r="I35" t="n">
-        <v>1.074</v>
+        <v>0.417</v>
       </c>
       <c r="J35" t="n">
-        <v>2.111</v>
+        <v>0.583</v>
       </c>
       <c r="K35" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.583</v>
       </c>
       <c r="L35" t="n">
-        <v>0.444</v>
+        <v>0.167</v>
       </c>
       <c r="M35" t="n">
-        <v>0.407</v>
+        <v>0.167</v>
       </c>
       <c r="N35" t="n">
-        <v>0.148</v>
+        <v>0.167</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.222</v>
+        <v>0.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.222</v>
+        <v>0.333</v>
       </c>
       <c r="R35" t="n">
-        <v>1.333</v>
+        <v>0.75</v>
       </c>
       <c r="S35" t="n">
-        <v>1.222</v>
+        <v>0.333</v>
       </c>
       <c r="T35" t="n">
-        <v>109</v>
+        <v>9</v>
       </c>
       <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
         <v>0.333</v>
       </c>
-      <c r="V35" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0.296</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.111</v>
-      </c>
       <c r="Z35" t="n">
-        <v>1.37</v>
+        <v>0.583</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.571</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.259</v>
+        <v>0.167</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.778</v>
+        <v>0.25</v>
       </c>
       <c r="AD35" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AI35" t="n">
         <v>0.333</v>
       </c>
-      <c r="AE35" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="AG35" t="n">
+      <c r="AJ35" t="n">
         <v>0.5</v>
       </c>
-      <c r="AH35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
       <c r="AK35" t="n">
-        <v>0.444</v>
+        <v>0.083</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.074</v>
+        <v>0.833</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.414</v>
+        <v>0.1</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>23:42</t>
+          <t>07:03</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>4.547</v>
+        <v>2.433</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.481</v>
+        <v>0.31</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.524</v>
+        <v>0.366</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.766</v>
+        <v>0.582</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.269</v>
+        <v>0.205</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.26</v>
+        <v>0.19</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.727</v>
+        <v>1.167</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.333</v>
+        <v>3.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.061</v>
+        <v>4.667</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.155</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.02</v>
+        <v>0.026</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.039</v>
+        <v>0.093</v>
       </c>
       <c r="BA35" t="n">
-        <v>0.067</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#6 X. LOPEZ-AROSTEGUI (Per Game)</t>
+          <t>#7 B. KEY (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C36" t="n">
-        <v>1.417</v>
+        <v>5.393</v>
       </c>
       <c r="D36" t="n">
-        <v>0.167</v>
+        <v>1.571</v>
       </c>
       <c r="E36" t="n">
-        <v>0.583</v>
+        <v>2.964</v>
       </c>
       <c r="F36" t="n">
-        <v>0.25</v>
+        <v>0.393</v>
       </c>
       <c r="G36" t="n">
-        <v>1.167</v>
+        <v>1.5</v>
       </c>
       <c r="H36" t="n">
+        <v>1.071</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.857</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.357</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2.393</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1.714</v>
+      </c>
+      <c r="T36" t="n">
+        <v>172</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>3.107</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="AG36" t="n">
         <v>0.333</v>
       </c>
-      <c r="I36" t="n">
-        <v>0.417</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="T36" t="n">
-        <v>9</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
       <c r="AH36" t="n">
-        <v>0.167</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.333</v>
+        <v>0.357</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.083</v>
+        <v>0.321</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.833</v>
+        <v>1.143</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.1</v>
+        <v>0.281</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>2.433</v>
+        <v>6.317</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.31</v>
+        <v>0.484</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.366</v>
+        <v>0.511</v>
       </c>
       <c r="AR36" t="n">
-        <v>0.582</v>
+        <v>0.854</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.205</v>
+        <v>0.164</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.167</v>
+        <v>0.931</v>
       </c>
       <c r="AV36" t="n">
-        <v>3.5</v>
+        <v>4.31</v>
       </c>
       <c r="AW36" t="n">
-        <v>4.667</v>
+        <v>5.241</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.114</v>
+        <v>0.176</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.019</v>
+        <v>0.065</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.165</v>
       </c>
       <c r="BA36" t="n">
-        <v>0.018</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#7 B. KEY (Per Game)</t>
+          <t>#8 J. MONTERO (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C37" t="n">
-        <v>5.393</v>
+        <v>13.688</v>
       </c>
       <c r="D37" t="n">
-        <v>1.571</v>
+        <v>2.562</v>
       </c>
       <c r="E37" t="n">
-        <v>2.964</v>
+        <v>5.219</v>
       </c>
       <c r="F37" t="n">
-        <v>0.393</v>
+        <v>1.719</v>
       </c>
       <c r="G37" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="H37" t="n">
-        <v>1.071</v>
+        <v>3.406</v>
       </c>
       <c r="I37" t="n">
-        <v>1.857</v>
+        <v>3.812</v>
       </c>
       <c r="J37" t="n">
-        <v>0.964</v>
+        <v>4.562</v>
       </c>
       <c r="K37" t="n">
-        <v>2.357</v>
+        <v>2.062</v>
       </c>
       <c r="L37" t="n">
-        <v>0.964</v>
+        <v>0.781</v>
       </c>
       <c r="M37" t="n">
-        <v>0.75</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>0.714</v>
+        <v>0.594</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.036</v>
+        <v>1.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.929</v>
+        <v>1.188</v>
       </c>
       <c r="R37" t="n">
-        <v>2.393</v>
+        <v>1.219</v>
       </c>
       <c r="S37" t="n">
-        <v>1.714</v>
+        <v>3.906</v>
       </c>
       <c r="T37" t="n">
-        <v>172</v>
+        <v>551</v>
       </c>
       <c r="U37" t="n">
-        <v>0.821</v>
+        <v>0.094</v>
       </c>
       <c r="V37" t="n">
-        <v>1.107</v>
+        <v>0.156</v>
       </c>
       <c r="W37" t="n">
-        <v>0.857</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0.536</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.321</v>
+        <v>4.719</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.107</v>
+        <v>5.656</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.747</v>
+        <v>0.834</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.286</v>
+        <v>1.062</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.821</v>
+        <v>2.531</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.348</v>
+        <v>0.42</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.036</v>
+        <v>0.188</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.107</v>
+        <v>0.438</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.333</v>
+        <v>0.429</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.125</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.357</v>
+        <v>0.344</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.2</v>
+        <v>0.364</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.321</v>
+        <v>1.594</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.143</v>
+        <v>5.156</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.281</v>
+        <v>0.309</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>26:02</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>6.317</v>
+        <v>13.646</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.484</v>
+        <v>0.48</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.511</v>
+        <v>0.552</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.854</v>
+        <v>1.003</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.164</v>
+        <v>0.092</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.24</v>
+        <v>0.318</v>
       </c>
       <c r="AU37" t="n">
-        <v>0.931</v>
+        <v>3.65</v>
       </c>
       <c r="AV37" t="n">
-        <v>4.31</v>
+        <v>8.574999999999999</v>
       </c>
       <c r="AW37" t="n">
-        <v>5.241</v>
+        <v>12.225</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.109</v>
+        <v>0.28</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.04</v>
+        <v>0.039</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0.102</v>
+        <v>0.106</v>
       </c>
       <c r="BA37" t="n">
-        <v>0.031</v>
+        <v>0.161</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>#8 J. MONTERO (Per Game)</t>
+          <t>#10 O. MOORE (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C38" t="n">
-        <v>13.688</v>
+        <v>8.395</v>
       </c>
       <c r="D38" t="n">
-        <v>2.562</v>
+        <v>2.289</v>
       </c>
       <c r="E38" t="n">
-        <v>5.219</v>
+        <v>4.395</v>
       </c>
       <c r="F38" t="n">
-        <v>1.719</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="H38" t="n">
-        <v>3.406</v>
+        <v>1.368</v>
       </c>
       <c r="I38" t="n">
-        <v>3.812</v>
+        <v>1.895</v>
       </c>
       <c r="J38" t="n">
-        <v>4.562</v>
+        <v>3.079</v>
       </c>
       <c r="K38" t="n">
-        <v>2.062</v>
+        <v>1.526</v>
       </c>
       <c r="L38" t="n">
-        <v>0.781</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.553</v>
       </c>
       <c r="N38" t="n">
-        <v>0.594</v>
+        <v>0.5</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.25</v>
+        <v>1.526</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.188</v>
+        <v>1.5</v>
       </c>
       <c r="R38" t="n">
-        <v>1.219</v>
+        <v>1.053</v>
       </c>
       <c r="S38" t="n">
-        <v>3.906</v>
+        <v>1.684</v>
       </c>
       <c r="T38" t="n">
-        <v>551</v>
+        <v>367</v>
       </c>
       <c r="U38" t="n">
-        <v>1.656</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.656</v>
+        <v>0.079</v>
       </c>
       <c r="W38" t="n">
-        <v>2.156</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.312</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>4.719</v>
+        <v>3.079</v>
       </c>
       <c r="Z38" t="n">
-        <v>5.656</v>
+        <v>4.184</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.834</v>
+        <v>0.736</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.062</v>
+        <v>0.526</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.531</v>
+        <v>1.447</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.42</v>
+        <v>0.364</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.188</v>
+        <v>0.053</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.438</v>
+        <v>0.132</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.429</v>
+        <v>0.4</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.125</v>
+        <v>0.132</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.344</v>
+        <v>0.316</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.364</v>
+        <v>0.417</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.594</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AL38" t="n">
-        <v>5.156</v>
+        <v>2.184</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.309</v>
+        <v>0.313</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>44:20</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>13.646</v>
+        <v>9.255000000000001</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.552</v>
+        <v>0.543</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.003</v>
+        <v>0.907</v>
       </c>
       <c r="AS38" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>2.017</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>4.517</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>6.534</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="AZ38" t="n">
         <v>0.092</v>
       </c>
-      <c r="AT38" t="n">
-        <v>0.318</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>8.574999999999999</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>12.225</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>0.052</v>
-      </c>
       <c r="BA38" t="n">
-        <v>0.161</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>#10 O. MOORE (Per Game)</t>
+          <t>#12 N. SAKO (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C39" t="n">
-        <v>8.395</v>
+        <v>4.972</v>
       </c>
       <c r="D39" t="n">
-        <v>2.289</v>
+        <v>2.083</v>
       </c>
       <c r="E39" t="n">
-        <v>4.395</v>
+        <v>3.444</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8159999999999999</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.368</v>
+        <v>0.806</v>
       </c>
       <c r="I39" t="n">
-        <v>1.895</v>
+        <v>1.75</v>
       </c>
       <c r="J39" t="n">
-        <v>3.079</v>
+        <v>0.611</v>
       </c>
       <c r="K39" t="n">
-        <v>1.526</v>
+        <v>1.972</v>
       </c>
       <c r="L39" t="n">
-        <v>0.8159999999999999</v>
+        <v>1.75</v>
       </c>
       <c r="M39" t="n">
-        <v>0.553</v>
+        <v>0.306</v>
       </c>
       <c r="N39" t="n">
-        <v>0.5</v>
+        <v>0.639</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1.526</v>
+        <v>0.833</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.5</v>
+        <v>0.778</v>
       </c>
       <c r="R39" t="n">
-        <v>1.053</v>
+        <v>1.556</v>
       </c>
       <c r="S39" t="n">
-        <v>1.684</v>
+        <v>1.75</v>
       </c>
       <c r="T39" t="n">
-        <v>367</v>
+        <v>263</v>
       </c>
       <c r="U39" t="n">
-        <v>1.105</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.5</v>
+        <v>0.056</v>
       </c>
       <c r="W39" t="n">
-        <v>0.763</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0.421</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>3.079</v>
+        <v>2.583</v>
       </c>
       <c r="Z39" t="n">
-        <v>4.184</v>
+        <v>3.333</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.736</v>
+        <v>0.775</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.526</v>
+        <v>0.278</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.447</v>
+        <v>0.806</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.364</v>
+        <v>0.345</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.053</v>
+        <v>0.028</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.132</v>
+        <v>0.111</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.132</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.316</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.417</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.6840000000000001</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>2.184</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.313</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>38:06</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>9.255000000000001</v>
+        <v>5.048</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.51</v>
+        <v>0.605</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.543</v>
+        <v>0.59</v>
       </c>
       <c r="AR39" t="n">
-        <v>0.907</v>
+        <v>0.985</v>
       </c>
       <c r="AS39" t="n">
         <v>0.165</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.198</v>
+        <v>0.234</v>
       </c>
       <c r="AU39" t="n">
-        <v>2.017</v>
+        <v>0.733</v>
       </c>
       <c r="AV39" t="n">
-        <v>4.517</v>
+        <v>4.133</v>
       </c>
       <c r="AW39" t="n">
-        <v>6.534</v>
+        <v>4.867</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.109</v>
+        <v>0.172</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.023</v>
+        <v>0.144</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0.045</v>
+        <v>0.168</v>
       </c>
       <c r="BA39" t="n">
-        <v>0.104</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>#12 N. SAKO (Per Game)</t>
+          <t>#13 D. THOMPSON (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C40" t="n">
-        <v>4.972</v>
+        <v>9.579000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>2.083</v>
+        <v>1.842</v>
       </c>
       <c r="E40" t="n">
-        <v>3.444</v>
+        <v>3.368</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>1.632</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H40" t="n">
-        <v>0.806</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>1.75</v>
+        <v>1.184</v>
       </c>
       <c r="J40" t="n">
-        <v>0.611</v>
+        <v>3.421</v>
       </c>
       <c r="K40" t="n">
-        <v>1.972</v>
+        <v>1.132</v>
       </c>
       <c r="L40" t="n">
-        <v>1.75</v>
+        <v>0.895</v>
       </c>
       <c r="M40" t="n">
-        <v>0.306</v>
+        <v>1</v>
       </c>
       <c r="N40" t="n">
-        <v>0.639</v>
+        <v>0.395</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.833</v>
+        <v>1.053</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.778</v>
+        <v>0.947</v>
       </c>
       <c r="R40" t="n">
-        <v>1.556</v>
+        <v>1.711</v>
       </c>
       <c r="S40" t="n">
-        <v>1.75</v>
+        <v>1.395</v>
       </c>
       <c r="T40" t="n">
-        <v>263</v>
+        <v>417</v>
       </c>
       <c r="U40" t="n">
-        <v>0.472</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.028</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.583</v>
+        <v>2.026</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.333</v>
+        <v>2.684</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.775</v>
+        <v>0.755</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.278</v>
+        <v>0.763</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.806</v>
+        <v>1.605</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.345</v>
+        <v>0.475</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.028</v>
+        <v>0.053</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.111</v>
+        <v>0.079</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.25</v>
+        <v>0.667</v>
       </c>
       <c r="AH40" t="n">
         <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>0.132</v>
       </c>
       <c r="AJ40" t="n">
         <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.632</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>3.868</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>0.422</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>24:07</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>5.048</v>
+        <v>8.942</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.605</v>
+        <v>0.582</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.59</v>
+        <v>0.607</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.985</v>
+        <v>1.071</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.165</v>
+        <v>0.118</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.234</v>
+        <v>0.136</v>
       </c>
       <c r="AU40" t="n">
-        <v>0.733</v>
+        <v>3.25</v>
       </c>
       <c r="AV40" t="n">
-        <v>4.133</v>
+        <v>7</v>
       </c>
       <c r="AW40" t="n">
-        <v>4.867</v>
+        <v>10.25</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.094</v>
+        <v>0.21</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.079</v>
+        <v>0.051</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0.092</v>
+        <v>0.067</v>
       </c>
       <c r="BA40" t="n">
-        <v>0.02</v>
+        <v>0.117</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>#13 D. THOMPSON (Per Game)</t>
+          <t>#18 I. IROEGBU (Per Game)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>9.579000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="D41" t="n">
-        <v>1.842</v>
+        <v>0.5</v>
       </c>
       <c r="E41" t="n">
-        <v>3.368</v>
+        <v>1.5</v>
       </c>
       <c r="F41" t="n">
-        <v>1.632</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="H41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R41" t="n">
         <v>1</v>
       </c>
-      <c r="I41" t="n">
-        <v>1.184</v>
-      </c>
-      <c r="J41" t="n">
-        <v>3.421</v>
-      </c>
-      <c r="K41" t="n">
-        <v>1.132</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="M41" t="n">
+      <c r="S41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T41" t="n">
+        <v>6</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA41" t="n">
         <v>1</v>
       </c>
-      <c r="N41" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>1.053</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0.947</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.711</v>
-      </c>
-      <c r="S41" t="n">
-        <v>1.395</v>
-      </c>
-      <c r="T41" t="n">
-        <v>417</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.447</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0.8159999999999999</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.079</v>
-      </c>
-      <c r="X41" t="n">
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AN41" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AO41" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.022</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="AT41" t="n">
         <v>0.5</v>
       </c>
-      <c r="Y41" t="n">
-        <v>2.026</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2.684</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>0.763</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.605</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>1.632</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>3.868</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>0.422</v>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>38:20</t>
-        </is>
-      </c>
-      <c r="AO41" t="n">
-        <v>8.942</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>0.582</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>1.071</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>0.136</v>
-      </c>
       <c r="AU41" t="n">
-        <v>3.25</v>
+        <v>0.333</v>
       </c>
       <c r="AV41" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AW41" t="n">
-        <v>10.25</v>
+        <v>2.333</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.105</v>
+        <v>0.196</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0.033</v>
+        <v>0</v>
       </c>
       <c r="BA41" t="n">
-        <v>0.117</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>#18 I. IROEGBU (Per Game)</t>
+          <t>#24 M. COSTELLO (Per Game)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="C42" t="n">
-        <v>5.5</v>
+        <v>6.529</v>
       </c>
       <c r="D42" t="n">
+        <v>1.059</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.618</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.206</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.559</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.882</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.676</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1.206</v>
+      </c>
+      <c r="T42" t="n">
+        <v>274</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.647</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.971</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="AD42" t="n">
         <v>0.5</v>
       </c>
-      <c r="E42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F42" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I42" t="n">
-        <v>2</v>
-      </c>
-      <c r="J42" t="n">
+      <c r="AE42" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="AI42" t="n">
         <v>0.5</v>
       </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1</v>
-      </c>
-      <c r="S42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T42" t="n">
-        <v>6</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1</v>
-      </c>
-      <c r="W42" t="n">
-        <v>2</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>0.471</v>
       </c>
       <c r="AK42" t="n">
-        <v>1</v>
+        <v>0.971</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.667</v>
+        <v>0.388</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>5.38</v>
+        <v>5.98</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.667</v>
+        <v>0.621</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.709</v>
+        <v>0.616</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.022</v>
+        <v>1.092</v>
       </c>
       <c r="AS42" t="n">
-        <v>0.279</v>
+        <v>0.113</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.5</v>
+        <v>0.172</v>
       </c>
       <c r="AU42" t="n">
-        <v>0.333</v>
+        <v>1.348</v>
       </c>
       <c r="AV42" t="n">
-        <v>2</v>
+        <v>6.826</v>
       </c>
       <c r="AW42" t="n">
-        <v>2.333</v>
+        <v>8.173999999999999</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.137</v>
+        <v>0.161</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>0.195</v>
       </c>
       <c r="BA42" t="n">
-        <v>0.016</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>#24 M. COSTELLO (Per Game)</t>
+          <t>#32 I. NOGUES (Per Game)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="C43" t="n">
-        <v>6.529</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>1.059</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1.618</v>
+        <v>0.111</v>
       </c>
       <c r="F43" t="n">
-        <v>1.206</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="T43" t="n">
+        <v>5</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN43" t="inlineStr">
+        <is>
+          <t>02:21</t>
+        </is>
+      </c>
+      <c r="AO43" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="n">
         <v>3</v>
       </c>
-      <c r="H43" t="n">
-        <v>0.794</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1.559</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0.912</v>
-      </c>
-      <c r="K43" t="n">
-        <v>2.882</v>
-      </c>
-      <c r="L43" t="n">
-        <v>1</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0.471</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0.529</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0.676</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.676</v>
-      </c>
-      <c r="S43" t="n">
-        <v>1.206</v>
-      </c>
-      <c r="T43" t="n">
-        <v>274</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0.529</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.176</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.412</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.647</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.971</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0.836</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>0.294</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0.471</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>0.971</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>34:26</t>
-        </is>
-      </c>
-      <c r="AO43" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>0.621</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>0.616</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>1.092</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>0.113</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>0.172</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>1.348</v>
-      </c>
       <c r="AV43" t="n">
-        <v>6.826</v>
+        <v>2</v>
       </c>
       <c r="AW43" t="n">
-        <v>8.173999999999999</v>
+        <v>5</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.078</v>
+        <v>0.064</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.032</v>
+        <v>0.051</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0.094</v>
+        <v>0.187</v>
       </c>
       <c r="BA43" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>#32 I. NOGUES (Per Game)</t>
+          <t>#77 Y. SIMA (Per Game)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>2.111</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="E44" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="F44" t="n">
         <v>0.111</v>
       </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
       <c r="G44" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="J44" t="n">
         <v>0.111</v>
       </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
         <v>0.333</v>
       </c>
-      <c r="K44" t="n">
-        <v>0.389</v>
-      </c>
       <c r="L44" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="M44" t="n">
         <v>0.111</v>
       </c>
-      <c r="M44" t="n">
-        <v>0.278</v>
-      </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.556</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="T44" t="n">
+        <v>9</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.222</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="n">
         <v>0.111</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="S44" t="n">
+      <c r="AL44" t="n">
         <v>0.333</v>
       </c>
-      <c r="T44" t="n">
-        <v>5</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>0.056</v>
-      </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>05:07</t>
+          <t>05:29</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>0.333</v>
+        <v>2.502</v>
       </c>
       <c r="AP44" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0</v>
+        <v>0.513</v>
       </c>
       <c r="AR44" t="n">
-        <v>0</v>
+        <v>0.844</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.333</v>
+        <v>0.178</v>
       </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>0.267</v>
       </c>
       <c r="AU44" t="n">
-        <v>3</v>
+        <v>0.25</v>
       </c>
       <c r="AV44" t="n">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="AW44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.029</v>
+        <v>0.205</v>
       </c>
       <c r="AY44" t="n">
-        <v>0.024</v>
+        <v>0.132</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.068</v>
       </c>
       <c r="BA44" t="n">
-        <v>0.01</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>#77 Y. SIMA (Per Game)</t>
+          <t>#77 N. SESTINA (Per Game)</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C45" t="n">
-        <v>2.111</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
         <v>0.667</v>
       </c>
-      <c r="E45" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.111</v>
-      </c>
       <c r="G45" t="n">
-        <v>0.333</v>
+        <v>3.333</v>
       </c>
       <c r="H45" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0.889</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0.111</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>0.333</v>
+        <v>1.667</v>
       </c>
       <c r="L45" t="n">
         <v>0.667</v>
       </c>
       <c r="M45" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1</v>
+      </c>
+      <c r="S45" t="n">
         <v>0.333</v>
       </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.556</v>
-      </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
         <v>0.667</v>
       </c>
-      <c r="T45" t="n">
-        <v>9</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
         <v>0.333</v>
       </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.111</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.222</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0.909</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0.556</v>
-      </c>
       <c r="AD45" t="n">
         <v>0</v>
       </c>
@@ -7524,91 +7524,91 @@
         <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK45" t="n">
-        <v>0.111</v>
+        <v>0.333</v>
       </c>
       <c r="AL45" t="n">
-        <v>0.333</v>
+        <v>2.667</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.333</v>
+        <v>0.125</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>2.502</v>
+        <v>4.333</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.5</v>
+        <v>0.231</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.513</v>
+        <v>0.231</v>
       </c>
       <c r="AR45" t="n">
-        <v>0.844</v>
+        <v>0.462</v>
       </c>
       <c r="AS45" t="n">
-        <v>0.178</v>
+        <v>0</v>
       </c>
       <c r="AT45" t="n">
-        <v>0.267</v>
+        <v>0</v>
       </c>
       <c r="AU45" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AV45" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AW45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.102</v>
+        <v>0.202</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.066</v>
+        <v>0.075</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0.034</v>
+        <v>0.195</v>
       </c>
       <c r="BA45" t="n">
-        <v>0.003</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>#77 N. SESTINA (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>3.333</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -7617,13 +7617,13 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>1.667</v>
+        <v>1.895</v>
       </c>
       <c r="L46" t="n">
-        <v>0.667</v>
+        <v>2.132</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -7635,25 +7635,25 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>0.447</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
         <v>0</v>
@@ -7665,7 +7665,7 @@
         <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -7674,7 +7674,7 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -7689,39 +7689,39 @@
         <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
-        <v>2.667</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>23:18</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>4.333</v>
+        <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.231</v>
+        <v>0</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.231</v>
+        <v>0</v>
       </c>
       <c r="AR46" t="n">
-        <v>0.462</v>
+        <v>0</v>
       </c>
       <c r="AS46" t="n">
         <v>0</v>
@@ -7739,178 +7739,178 @@
         <v>0</v>
       </c>
       <c r="AX46" t="n">
-        <v>0.08400000000000001</v>
+        <v>0</v>
       </c>
       <c r="AY46" t="n">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0.081</v>
+        <v>0</v>
       </c>
       <c r="BA46" t="n">
-        <v>0.031</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>38</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>90.895</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>20.921</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>36.553</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>11.684</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>31.842</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>19.421</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>21.026</v>
       </c>
       <c r="K47" t="n">
-        <v>1.895</v>
+        <v>24.711</v>
       </c>
       <c r="L47" t="n">
-        <v>2.132</v>
+        <v>12.974</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>6.921</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>5.553</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0.447</v>
+        <v>12.632</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>11.605</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>18.868</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>20.474</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>4174</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>0.342</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>0.132</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>28.737</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>35.474</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>5.184</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>12.684</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>0.409</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>2.395</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>0.418</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.711</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>4.447</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>0.385</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>9.974</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>27.395</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>0.364</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>201:18</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>0</v>
+        <v>89.572</v>
       </c>
       <c r="AP47" t="n">
-        <v>0</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0</v>
+        <v>0.591</v>
       </c>
       <c r="AR47" t="n">
-        <v>0</v>
+        <v>1.015</v>
       </c>
       <c r="AS47" t="n">
-        <v>0</v>
+        <v>0.141</v>
       </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>0.205</v>
       </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>1.665</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>5.415</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>7.079</v>
       </c>
       <c r="AX47" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="BA47" t="n">
         <v>0</v>
@@ -7919,495 +7919,165 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>38</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>86.316</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>20.947</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>38.053</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>27.342</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>15.921</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>19.579</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>19.395</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>10.974</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>6.684</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>5.553</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>13.263</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>11.842</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>20.658</v>
       </c>
       <c r="T48" t="n">
-        <v>136</v>
+        <v>3922</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>0.132</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>0.237</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>0.368</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>0.158</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>29.684</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>37.105</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>6.079</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>14.474</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.105</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>2.395</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>0.462</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.289</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>3.421</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>0.377</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>8.211</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>23.921</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>0.343</v>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>201:18</t>
         </is>
       </c>
       <c r="AO48" t="n">
-        <v>0.447</v>
+        <v>87.273</v>
       </c>
       <c r="AP48" t="n">
-        <v>0</v>
+        <v>0.538</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>0.583</v>
       </c>
       <c r="AR48" t="n">
-        <v>0</v>
+        <v>0.989</v>
       </c>
       <c r="AS48" t="n">
-        <v>0</v>
+        <v>0.152</v>
       </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>0.243</v>
       </c>
       <c r="AU48" t="n">
-        <v>0</v>
+        <v>1.462</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>4.931</v>
       </c>
       <c r="AW48" t="n">
-        <v>0</v>
+        <v>6.393</v>
       </c>
       <c r="AX48" t="n">
-        <v>0</v>
+        <v>0.195</v>
       </c>
       <c r="AY48" t="n">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="BA48" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>38</v>
-      </c>
-      <c r="C49" t="n">
-        <v>90.895</v>
-      </c>
-      <c r="D49" t="n">
-        <v>20.921</v>
-      </c>
-      <c r="E49" t="n">
-        <v>36.553</v>
-      </c>
-      <c r="F49" t="n">
-        <v>11.684</v>
-      </c>
-      <c r="G49" t="n">
-        <v>31.842</v>
-      </c>
-      <c r="H49" t="n">
-        <v>14</v>
-      </c>
-      <c r="I49" t="n">
-        <v>19.421</v>
-      </c>
-      <c r="J49" t="n">
-        <v>21.026</v>
-      </c>
-      <c r="K49" t="n">
-        <v>24.711</v>
-      </c>
-      <c r="L49" t="n">
-        <v>12.974</v>
-      </c>
-      <c r="M49" t="n">
-        <v>6.921</v>
-      </c>
-      <c r="N49" t="n">
-        <v>5.553</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>12.632</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>11.605</v>
-      </c>
-      <c r="R49" t="n">
-        <v>18.868</v>
-      </c>
-      <c r="S49" t="n">
-        <v>20.474</v>
-      </c>
-      <c r="T49" t="n">
-        <v>4174</v>
-      </c>
-      <c r="U49" t="n">
-        <v>9.946999999999999</v>
-      </c>
-      <c r="V49" t="n">
-        <v>13.158</v>
-      </c>
-      <c r="W49" t="n">
-        <v>11.789</v>
-      </c>
-      <c r="X49" t="n">
-        <v>6.447</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>28.737</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>35.474</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>5.184</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>12.684</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0.409</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>2.395</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.711</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>4.447</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>9.974</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>27.395</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>201:18</t>
-        </is>
-      </c>
-      <c r="AO49" t="n">
-        <v>89.572</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>0.591</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>1.015</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>1.665</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>5.415</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>7.079</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY49" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AZ49" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="BA49" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>38</v>
-      </c>
-      <c r="C50" t="n">
-        <v>86.316</v>
-      </c>
-      <c r="D50" t="n">
-        <v>20.947</v>
-      </c>
-      <c r="E50" t="n">
-        <v>38.053</v>
-      </c>
-      <c r="F50" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G50" t="n">
-        <v>27.342</v>
-      </c>
-      <c r="H50" t="n">
-        <v>15.921</v>
-      </c>
-      <c r="I50" t="n">
-        <v>19.579</v>
-      </c>
-      <c r="J50" t="n">
-        <v>19.395</v>
-      </c>
-      <c r="K50" t="n">
-        <v>24</v>
-      </c>
-      <c r="L50" t="n">
-        <v>10.974</v>
-      </c>
-      <c r="M50" t="n">
-        <v>6.684</v>
-      </c>
-      <c r="N50" t="n">
-        <v>5.553</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>13.263</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>11.842</v>
-      </c>
-      <c r="R50" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="S50" t="n">
-        <v>20.658</v>
-      </c>
-      <c r="T50" t="n">
-        <v>3922</v>
-      </c>
-      <c r="U50" t="n">
-        <v>8.368</v>
-      </c>
-      <c r="V50" t="n">
-        <v>11.132</v>
-      </c>
-      <c r="W50" t="n">
-        <v>9.026</v>
-      </c>
-      <c r="X50" t="n">
-        <v>5.553</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>29.684</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>37.105</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>6.079</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>14.474</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1.105</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>2.395</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1.289</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>3.421</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>0.377</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>8.211</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>23.921</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>0.343</v>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>201:18</t>
-        </is>
-      </c>
-      <c r="AO50" t="n">
-        <v>87.273</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>0.989</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>0.152</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>0.243</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>1.462</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>4.931</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>6.393</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="BA50" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_VALENCIA BASKET.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_VALENCIA BASKET.xlsx
@@ -671,13 +671,13 @@
         <v>0.2046941131204309</v>
       </c>
       <c r="J2" t="n">
-        <v>13</v>
+        <v>394</v>
       </c>
       <c r="K2" t="n">
-        <v>19</v>
+        <v>510</v>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>468</v>
       </c>
       <c r="M2" t="n">
         <v>441</v>
@@ -752,13 +752,13 @@
         <v>1.100826446280992</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.02579365079365079</v>
+        <v>0.7817460317460317</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.0385395537525355</v>
+        <v>1.03448275862069</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.5</v>
+        <v>1.786259541984733</v>
       </c>
       <c r="AN2" t="n">
         <v>1.664583333333333</v>
@@ -801,13 +801,13 @@
         <v>0.204694113120431</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3421052631578947</v>
+        <v>10.36842105263158</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5</v>
+        <v>13.42105263157895</v>
       </c>
       <c r="L3" t="n">
-        <v>0.131578947368421</v>
+        <v>12.31578947368421</v>
       </c>
       <c r="M3" t="n">
         <v>11.60526315789474</v>
@@ -882,13 +882,13 @@
         <v>1.100826446280992</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.02579365079365079</v>
+        <v>0.7817460317460317</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0385395537525355</v>
+        <v>1.03448275862069</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.5</v>
+        <v>1.786259541984733</v>
       </c>
       <c r="AN3" t="n">
         <v>1.664583333333333</v>
@@ -931,13 +931,13 @@
         <v>0.2434607645875252</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>336</v>
       </c>
       <c r="K4" t="n">
-        <v>9</v>
+        <v>435</v>
       </c>
       <c r="L4" t="n">
-        <v>14</v>
+        <v>356</v>
       </c>
       <c r="M4" t="n">
         <v>450</v>
@@ -1012,13 +1012,13 @@
         <v>1.042348411934553</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.01041666666666667</v>
+        <v>0.7</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.02158273381294964</v>
+        <v>1.043165467625899</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.333333333333333</v>
+        <v>1.596412556053812</v>
       </c>
       <c r="AN4" t="n">
         <v>1.462301587301587</v>
@@ -1061,13 +1061,13 @@
         <v>0.2434607645875252</v>
       </c>
       <c r="J5" t="n">
-        <v>0.131578947368421</v>
+        <v>8.842105263157896</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2368421052631579</v>
+        <v>11.44736842105263</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3684210526315789</v>
+        <v>9.368421052631579</v>
       </c>
       <c r="M5" t="n">
         <v>11.8421052631579</v>
@@ -1142,13 +1142,13 @@
         <v>1.042348411934552</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.01041666666666667</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.02158273381294964</v>
+        <v>1.043165467625899</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.333333333333333</v>
+        <v>1.596412556053812</v>
       </c>
       <c r="AN5" t="n">
         <v>1.462301587301587</v>
@@ -1486,16 +1486,16 @@
         <v>323</v>
       </c>
       <c r="U8" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="V8" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="W8" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="Y8" t="n">
         <v>92</v>
@@ -1651,16 +1651,16 @@
         <v>490</v>
       </c>
       <c r="U9" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="Y9" t="n">
         <v>128</v>
@@ -1816,16 +1816,16 @@
         <v>200</v>
       </c>
       <c r="U10" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="Y10" t="n">
         <v>38</v>
@@ -1981,16 +1981,16 @@
         <v>458</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="V11" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Y11" t="n">
         <v>145</v>
@@ -2146,16 +2146,16 @@
         <v>382</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y12" t="n">
         <v>82</v>
@@ -2311,16 +2311,16 @@
         <v>109</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y13" t="n">
         <v>30</v>
@@ -2482,10 +2482,10 @@
         <v>2</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="n">
         <v>4</v>
@@ -2641,16 +2641,16 @@
         <v>172</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y15" t="n">
         <v>65</v>
@@ -2806,16 +2806,16 @@
         <v>551</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="V16" t="n">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="Y16" t="n">
         <v>151</v>
@@ -2971,16 +2971,16 @@
         <v>367</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="V17" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Y17" t="n">
         <v>117</v>
@@ -3136,16 +3136,16 @@
         <v>263</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="V18" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y18" t="n">
         <v>93</v>
@@ -3301,16 +3301,16 @@
         <v>417</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y19" t="n">
         <v>77</v>
@@ -3469,13 +3469,13 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="n">
         <v>4</v>
@@ -3631,16 +3631,16 @@
         <v>274</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Y21" t="n">
         <v>56</v>
@@ -3964,7 +3964,7 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -4129,7 +4129,7 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
@@ -4456,16 +4456,16 @@
         <v>4174</v>
       </c>
       <c r="U26" t="n">
-        <v>13</v>
+        <v>394</v>
       </c>
       <c r="V26" t="n">
-        <v>19</v>
+        <v>510</v>
       </c>
       <c r="W26" t="n">
-        <v>5</v>
+        <v>468</v>
       </c>
       <c r="X26" t="n">
-        <v>2</v>
+        <v>262</v>
       </c>
       <c r="Y26" t="n">
         <v>1092</v>
@@ -4621,16 +4621,16 @@
         <v>3922</v>
       </c>
       <c r="U27" t="n">
-        <v>5</v>
+        <v>336</v>
       </c>
       <c r="V27" t="n">
-        <v>9</v>
+        <v>435</v>
       </c>
       <c r="W27" t="n">
-        <v>14</v>
+        <v>356</v>
       </c>
       <c r="X27" t="n">
-        <v>6</v>
+        <v>223</v>
       </c>
       <c r="Y27" t="n">
         <v>1128</v>
@@ -4845,16 +4845,16 @@
         <v>323</v>
       </c>
       <c r="U29" t="n">
-        <v>0.147</v>
+        <v>0.618</v>
       </c>
       <c r="V29" t="n">
-        <v>0.059</v>
+        <v>1.853</v>
       </c>
       <c r="W29" t="n">
-        <v>0.08799999999999999</v>
+        <v>1.412</v>
       </c>
       <c r="X29" t="n">
-        <v>0.029</v>
+        <v>0.765</v>
       </c>
       <c r="Y29" t="n">
         <v>2.706</v>
@@ -5010,16 +5010,16 @@
         <v>490</v>
       </c>
       <c r="U30" t="n">
-        <v>0.059</v>
+        <v>2.029</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.941</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.882</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>0.912</v>
       </c>
       <c r="Y30" t="n">
         <v>3.765</v>
@@ -5175,16 +5175,16 @@
         <v>200</v>
       </c>
       <c r="U31" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.486</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>0.371</v>
       </c>
       <c r="W31" t="n">
-        <v>0.057</v>
+        <v>0.771</v>
       </c>
       <c r="X31" t="n">
-        <v>0.029</v>
+        <v>0.429</v>
       </c>
       <c r="Y31" t="n">
         <v>1.086</v>
@@ -5340,16 +5340,16 @@
         <v>458</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>0.842</v>
       </c>
       <c r="V32" t="n">
-        <v>0.132</v>
+        <v>1.289</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.342</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>0.842</v>
       </c>
       <c r="Y32" t="n">
         <v>3.816</v>
@@ -5505,16 +5505,16 @@
         <v>382</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>0.658</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.079</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>0.658</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>0.368</v>
       </c>
       <c r="Y33" t="n">
         <v>2.158</v>
@@ -5670,16 +5670,16 @@
         <v>109</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>0.296</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>0.185</v>
       </c>
       <c r="Y34" t="n">
         <v>1.111</v>
@@ -5841,10 +5841,10 @@
         <v>0.167</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="Y35" t="n">
         <v>0.333</v>
@@ -6000,16 +6000,16 @@
         <v>172</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>0.964</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.107</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>0.857</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>0.536</v>
       </c>
       <c r="Y36" t="n">
         <v>2.321</v>
@@ -6165,16 +6165,16 @@
         <v>551</v>
       </c>
       <c r="U37" t="n">
-        <v>0.094</v>
+        <v>1.781</v>
       </c>
       <c r="V37" t="n">
-        <v>0.156</v>
+        <v>1.656</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>2.281</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.438</v>
       </c>
       <c r="Y37" t="n">
         <v>4.719</v>
@@ -6330,16 +6330,16 @@
         <v>367</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.237</v>
       </c>
       <c r="V38" t="n">
-        <v>0.079</v>
+        <v>1.526</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>0.895</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Y38" t="n">
         <v>3.079</v>
@@ -6495,16 +6495,16 @@
         <v>263</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>0.472</v>
       </c>
       <c r="V39" t="n">
-        <v>0.056</v>
+        <v>1.028</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="Y39" t="n">
         <v>2.583</v>
@@ -6660,16 +6660,16 @@
         <v>417</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.447</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.158</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>0.579</v>
       </c>
       <c r="Y40" t="n">
         <v>2.026</v>
@@ -6828,13 +6828,13 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
         <v>2</v>
@@ -6990,16 +6990,16 @@
         <v>274</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>0.529</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.265</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.412</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>0.735</v>
       </c>
       <c r="Y42" t="n">
         <v>1.647</v>
@@ -7323,7 +7323,7 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
@@ -7488,7 +7488,7 @@
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W45" t="n">
         <v>0</v>
@@ -7815,16 +7815,16 @@
         <v>4174</v>
       </c>
       <c r="U47" t="n">
-        <v>0.342</v>
+        <v>10.368</v>
       </c>
       <c r="V47" t="n">
-        <v>0.5</v>
+        <v>13.421</v>
       </c>
       <c r="W47" t="n">
-        <v>0.132</v>
+        <v>12.316</v>
       </c>
       <c r="X47" t="n">
-        <v>0.053</v>
+        <v>6.895</v>
       </c>
       <c r="Y47" t="n">
         <v>28.737</v>
@@ -7980,16 +7980,16 @@
         <v>3922</v>
       </c>
       <c r="U48" t="n">
-        <v>0.132</v>
+        <v>8.842000000000001</v>
       </c>
       <c r="V48" t="n">
-        <v>0.237</v>
+        <v>11.447</v>
       </c>
       <c r="W48" t="n">
-        <v>0.368</v>
+        <v>9.368</v>
       </c>
       <c r="X48" t="n">
-        <v>0.158</v>
+        <v>5.868</v>
       </c>
       <c r="Y48" t="n">
         <v>29.684</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_VALENCIA BASKET.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_VALENCIA BASKET.xlsx
@@ -683,13 +683,13 @@
         <v>441</v>
       </c>
       <c r="N2" t="n">
-        <v>1092</v>
+        <v>560</v>
       </c>
       <c r="O2" t="n">
-        <v>1348</v>
+        <v>816</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5186610234705656</v>
+        <v>0.3139669103501347</v>
       </c>
       <c r="Q2" t="n">
         <v>197</v>
@@ -710,25 +710,25 @@
         <v>0.03501346671796845</v>
       </c>
       <c r="W2" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="X2" t="n">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.06502500961908426</v>
+        <v>0.06925740669488265</v>
       </c>
       <c r="Z2" t="n">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AA2" t="n">
-        <v>1041</v>
+        <v>1030</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.400538668718738</v>
+        <v>0.3963062716429396</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8100890207715133</v>
+        <v>0.6862745098039216</v>
       </c>
       <c r="AD2" t="n">
         <v>0.4087136929460581</v>
@@ -737,13 +737,13 @@
         <v>0.4175824175824176</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.3722222222222222</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3640730067243035</v>
+        <v>0.3660194174757281</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.620178041543027</v>
+        <v>1.372549019607843</v>
       </c>
       <c r="AI2" t="n">
         <v>0.8351648351648352</v>
@@ -813,13 +813,13 @@
         <v>11.60526315789474</v>
       </c>
       <c r="N3" t="n">
-        <v>28.73684210526316</v>
+        <v>14.73684210526316</v>
       </c>
       <c r="O3" t="n">
-        <v>35.47368421052632</v>
+        <v>21.47368421052632</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5186610234705656</v>
+        <v>0.3139669103501347</v>
       </c>
       <c r="Q3" t="n">
         <v>5.184210526315789</v>
@@ -840,25 +840,25 @@
         <v>0.03501346671796846</v>
       </c>
       <c r="W3" t="n">
-        <v>1.710526315789474</v>
+        <v>1.763157894736842</v>
       </c>
       <c r="X3" t="n">
-        <v>4.447368421052632</v>
+        <v>4.736842105263158</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.06502500961908426</v>
+        <v>0.06925740669488265</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.973684210526315</v>
+        <v>9.921052631578947</v>
       </c>
       <c r="AA3" t="n">
-        <v>27.39473684210526</v>
+        <v>27.10526315789474</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.400538668718738</v>
+        <v>0.3963062716429396</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8100890207715133</v>
+        <v>0.6862745098039216</v>
       </c>
       <c r="AD3" t="n">
         <v>0.4087136929460581</v>
@@ -867,13 +867,13 @@
         <v>0.4175824175824175</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.3722222222222222</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3640730067243035</v>
+        <v>0.3660194174757281</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.620178041543027</v>
+        <v>1.372549019607843</v>
       </c>
       <c r="AI3" t="n">
         <v>0.8351648351648351</v>
@@ -943,13 +943,13 @@
         <v>450</v>
       </c>
       <c r="N4" t="n">
-        <v>1128</v>
+        <v>523</v>
       </c>
       <c r="O4" t="n">
-        <v>1410</v>
+        <v>805</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5674044265593562</v>
+        <v>0.323943661971831</v>
       </c>
       <c r="Q4" t="n">
         <v>231</v>
@@ -970,25 +970,25 @@
         <v>0.03661971830985915</v>
       </c>
       <c r="W4" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="X4" t="n">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0523138832997988</v>
+        <v>0.05955734406438632</v>
       </c>
       <c r="Z4" t="n">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="AA4" t="n">
-        <v>909</v>
+        <v>891</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.36579476861167</v>
+        <v>0.3585513078470825</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8</v>
+        <v>0.6496894409937888</v>
       </c>
       <c r="AD4" t="n">
         <v>0.42</v>
@@ -997,13 +997,13 @@
         <v>0.4615384615384616</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3769230769230769</v>
+        <v>0.3851351351351351</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3432343234323432</v>
+        <v>0.3411896745230079</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.6</v>
+        <v>1.299378881987578</v>
       </c>
       <c r="AI4" t="n">
         <v>0.9230769230769231</v>
@@ -1073,13 +1073,13 @@
         <v>11.8421052631579</v>
       </c>
       <c r="N5" t="n">
-        <v>29.68421052631579</v>
+        <v>13.76315789473684</v>
       </c>
       <c r="O5" t="n">
-        <v>37.10526315789474</v>
+        <v>21.18421052631579</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5674044265593562</v>
+        <v>0.3239436619718311</v>
       </c>
       <c r="Q5" t="n">
         <v>6.078947368421052</v>
@@ -1100,25 +1100,25 @@
         <v>0.03661971830985916</v>
       </c>
       <c r="W5" t="n">
-        <v>1.289473684210526</v>
+        <v>1.5</v>
       </c>
       <c r="X5" t="n">
-        <v>3.421052631578947</v>
+        <v>3.894736842105263</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0523138832997988</v>
+        <v>0.05955734406438632</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.210526315789474</v>
+        <v>8</v>
       </c>
       <c r="AA5" t="n">
-        <v>23.92105263157895</v>
+        <v>23.44736842105263</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.36579476861167</v>
+        <v>0.3585513078470825</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.6496894409937888</v>
       </c>
       <c r="AD5" t="n">
         <v>0.42</v>
@@ -1127,19 +1127,19 @@
         <v>0.4615384615384616</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3769230769230769</v>
+        <v>0.3851351351351351</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3432343234323432</v>
+        <v>0.3411896745230079</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.6</v>
+        <v>1.299378881987578</v>
       </c>
       <c r="AI5" t="n">
         <v>0.9230769230769231</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.042348411934552</v>
+        <v>1.042348411934553</v>
       </c>
       <c r="AK5" t="n">
         <v>0.7000000000000001</v>
@@ -1498,13 +1498,13 @@
         <v>26</v>
       </c>
       <c r="Y8" t="n">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="Z8" t="n">
-        <v>110</v>
+        <v>61</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.836</v>
+        <v>0.705</v>
       </c>
       <c r="AB8" t="n">
         <v>19</v>
@@ -1528,19 +1528,19 @@
         <v>14</v>
       </c>
       <c r="AI8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.583</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AK8" t="n">
         <v>49</v>
       </c>
       <c r="AL8" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.322</v>
+        <v>0.325</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
@@ -1663,13 +1663,13 @@
         <v>31</v>
       </c>
       <c r="Y9" t="n">
-        <v>128</v>
+        <v>62</v>
       </c>
       <c r="Z9" t="n">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.883</v>
+        <v>0.785</v>
       </c>
       <c r="AB9" t="n">
         <v>20</v>
@@ -1690,22 +1690,22 @@
         <v>0.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.429</v>
+        <v>0.417</v>
       </c>
       <c r="AK9" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AL9" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.394</v>
+        <v>0.396</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
@@ -1828,13 +1828,13 @@
         <v>15</v>
       </c>
       <c r="Y10" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="Z10" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.826</v>
+        <v>0.704</v>
       </c>
       <c r="AB10" t="n">
         <v>5</v>
@@ -1993,13 +1993,13 @@
         <v>32</v>
       </c>
       <c r="Y11" t="n">
-        <v>145</v>
+        <v>82</v>
       </c>
       <c r="Z11" t="n">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.879</v>
+        <v>0.804</v>
       </c>
       <c r="AB11" t="n">
         <v>19</v>
@@ -2158,13 +2158,13 @@
         <v>14</v>
       </c>
       <c r="Y12" t="n">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="Z12" t="n">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.788</v>
+        <v>0.741</v>
       </c>
       <c r="AB12" t="n">
         <v>19</v>
@@ -2185,22 +2185,22 @@
         <v>1</v>
       </c>
       <c r="AH12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.25</v>
+        <v>0.269</v>
       </c>
       <c r="AK12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL12" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.388</v>
+        <v>0.383</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
@@ -2323,13 +2323,13 @@
         <v>5</v>
       </c>
       <c r="Y13" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="Z13" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.588</v>
       </c>
       <c r="AB13" t="n">
         <v>7</v>
@@ -2488,13 +2488,13 @@
         <v>2</v>
       </c>
       <c r="Y14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>2</v>
@@ -2518,19 +2518,19 @@
         <v>2</v>
       </c>
       <c r="AI14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AK14" t="n">
         <v>1</v>
       </c>
       <c r="AL14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.1</v>
+        <v>0.111</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
@@ -2653,13 +2653,13 @@
         <v>15</v>
       </c>
       <c r="Y15" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="Z15" t="n">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.747</v>
+        <v>0.614</v>
       </c>
       <c r="AB15" t="n">
         <v>8</v>
@@ -2683,19 +2683,19 @@
         <v>2</v>
       </c>
       <c r="AI15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.2</v>
+        <v>0.182</v>
       </c>
       <c r="AK15" t="n">
         <v>9</v>
       </c>
       <c r="AL15" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.281</v>
+        <v>0.29</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
@@ -2818,13 +2818,13 @@
         <v>46</v>
       </c>
       <c r="Y16" t="n">
-        <v>151</v>
+        <v>42</v>
       </c>
       <c r="Z16" t="n">
-        <v>181</v>
+        <v>72</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.834</v>
+        <v>0.583</v>
       </c>
       <c r="AB16" t="n">
         <v>34</v>
@@ -2983,13 +2983,13 @@
         <v>19</v>
       </c>
       <c r="Y17" t="n">
-        <v>117</v>
+        <v>65</v>
       </c>
       <c r="Z17" t="n">
-        <v>159</v>
+        <v>107</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.736</v>
+        <v>0.607</v>
       </c>
       <c r="AB17" t="n">
         <v>20</v>
@@ -3013,19 +3013,19 @@
         <v>5</v>
       </c>
       <c r="AI17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.417</v>
+        <v>0.385</v>
       </c>
       <c r="AK17" t="n">
         <v>26</v>
       </c>
       <c r="AL17" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.313</v>
+        <v>0.317</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
@@ -3148,13 +3148,13 @@
         <v>8</v>
       </c>
       <c r="Y18" t="n">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="Z18" t="n">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.775</v>
+        <v>0.703</v>
       </c>
       <c r="AB18" t="n">
         <v>10</v>
@@ -3313,13 +3313,13 @@
         <v>22</v>
       </c>
       <c r="Y19" t="n">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="Z19" t="n">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.755</v>
+        <v>0.609</v>
       </c>
       <c r="AB19" t="n">
         <v>29</v>
@@ -3478,10 +3478,10 @@
         <v>2</v>
       </c>
       <c r="Y20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AA20" t="n">
         <v>1</v>
@@ -3643,13 +3643,13 @@
         <v>25</v>
       </c>
       <c r="Y21" t="n">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="Z21" t="n">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.836</v>
+        <v>0.725</v>
       </c>
       <c r="AB21" t="n">
         <v>5</v>
@@ -3673,19 +3673,19 @@
         <v>8</v>
       </c>
       <c r="AI21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.471</v>
+        <v>0.444</v>
       </c>
       <c r="AK21" t="n">
         <v>33</v>
       </c>
       <c r="AL21" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.388</v>
+        <v>0.393</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
@@ -3973,13 +3973,13 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z23" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.909</v>
+        <v>0.857</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -4168,19 +4168,19 @@
         <v>1</v>
       </c>
       <c r="AI24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AK24" t="n">
         <v>1</v>
       </c>
       <c r="AL24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.125</v>
+        <v>0.143</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
@@ -4468,13 +4468,13 @@
         <v>262</v>
       </c>
       <c r="Y26" t="n">
-        <v>1092</v>
+        <v>560</v>
       </c>
       <c r="Z26" t="n">
-        <v>1348</v>
+        <v>816</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="AB26" t="n">
         <v>197</v>
@@ -4495,22 +4495,22 @@
         <v>0.418</v>
       </c>
       <c r="AH26" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AI26" t="n">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.385</v>
+        <v>0.372</v>
       </c>
       <c r="AK26" t="n">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AL26" t="n">
-        <v>1041</v>
+        <v>1030</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.364</v>
+        <v>0.366</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>223</v>
       </c>
       <c r="Y27" t="n">
-        <v>1128</v>
+        <v>523</v>
       </c>
       <c r="Z27" t="n">
-        <v>1410</v>
+        <v>805</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.8</v>
+        <v>0.65</v>
       </c>
       <c r="AB27" t="n">
         <v>231</v>
@@ -4660,22 +4660,22 @@
         <v>0.462</v>
       </c>
       <c r="AH27" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="AI27" t="n">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.377</v>
+        <v>0.385</v>
       </c>
       <c r="AK27" t="n">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="AL27" t="n">
-        <v>909</v>
+        <v>891</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.343</v>
+        <v>0.341</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
@@ -4857,13 +4857,13 @@
         <v>0.765</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.706</v>
+        <v>1.265</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.235</v>
+        <v>1.794</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.836</v>
+        <v>0.705</v>
       </c>
       <c r="AB29" t="n">
         <v>0.5590000000000001</v>
@@ -4887,19 +4887,19 @@
         <v>0.412</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.706</v>
+        <v>0.735</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.583</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AK29" t="n">
         <v>1.441</v>
       </c>
       <c r="AL29" t="n">
-        <v>4.471</v>
+        <v>4.441</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.322</v>
+        <v>0.325</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
@@ -5022,13 +5022,13 @@
         <v>0.912</v>
       </c>
       <c r="Y30" t="n">
-        <v>3.765</v>
+        <v>1.824</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.265</v>
+        <v>2.324</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.883</v>
+        <v>0.785</v>
       </c>
       <c r="AB30" t="n">
         <v>0.588</v>
@@ -5049,22 +5049,22 @@
         <v>0.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.265</v>
+        <v>0.294</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.618</v>
+        <v>0.706</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.429</v>
+        <v>0.417</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.265</v>
+        <v>1.235</v>
       </c>
       <c r="AL30" t="n">
-        <v>3.206</v>
+        <v>3.118</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.394</v>
+        <v>0.396</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
@@ -5187,13 +5187,13 @@
         <v>0.429</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.086</v>
+        <v>0.543</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.314</v>
+        <v>0.771</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.826</v>
+        <v>0.704</v>
       </c>
       <c r="AB31" t="n">
         <v>0.143</v>
@@ -5352,13 +5352,13 @@
         <v>0.842</v>
       </c>
       <c r="Y32" t="n">
-        <v>3.816</v>
+        <v>2.158</v>
       </c>
       <c r="Z32" t="n">
-        <v>4.342</v>
+        <v>2.684</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.879</v>
+        <v>0.804</v>
       </c>
       <c r="AB32" t="n">
         <v>0.5</v>
@@ -5517,13 +5517,13 @@
         <v>0.368</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.158</v>
+        <v>1.658</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.737</v>
+        <v>2.237</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.788</v>
+        <v>0.741</v>
       </c>
       <c r="AB33" t="n">
         <v>0.5</v>
@@ -5544,22 +5544,22 @@
         <v>1</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.158</v>
+        <v>0.184</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.632</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.25</v>
+        <v>0.269</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.5</v>
+        <v>0.474</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.289</v>
+        <v>1.237</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.388</v>
+        <v>0.383</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
@@ -5682,13 +5682,13 @@
         <v>0.185</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.111</v>
+        <v>0.37</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.37</v>
+        <v>0.63</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.588</v>
       </c>
       <c r="AB34" t="n">
         <v>0.259</v>
@@ -5847,13 +5847,13 @@
         <v>0.167</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.583</v>
+        <v>0.25</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
         <v>0.167</v>
@@ -5877,19 +5877,19 @@
         <v>0.167</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.333</v>
+        <v>0.417</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AK35" t="n">
         <v>0.083</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.833</v>
+        <v>0.75</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.1</v>
+        <v>0.111</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
@@ -6012,13 +6012,13 @@
         <v>0.536</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.321</v>
+        <v>1.25</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.107</v>
+        <v>2.036</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.747</v>
+        <v>0.614</v>
       </c>
       <c r="AB36" t="n">
         <v>0.286</v>
@@ -6042,19 +6042,19 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.357</v>
+        <v>0.393</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.2</v>
+        <v>0.182</v>
       </c>
       <c r="AK36" t="n">
         <v>0.321</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.143</v>
+        <v>1.107</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.281</v>
+        <v>0.29</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
@@ -6177,13 +6177,13 @@
         <v>1.438</v>
       </c>
       <c r="Y37" t="n">
-        <v>4.719</v>
+        <v>1.312</v>
       </c>
       <c r="Z37" t="n">
-        <v>5.656</v>
+        <v>2.25</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.834</v>
+        <v>0.583</v>
       </c>
       <c r="AB37" t="n">
         <v>1.062</v>
@@ -6342,13 +6342,13 @@
         <v>0.5</v>
       </c>
       <c r="Y38" t="n">
-        <v>3.079</v>
+        <v>1.711</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.184</v>
+        <v>2.816</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.736</v>
+        <v>0.607</v>
       </c>
       <c r="AB38" t="n">
         <v>0.526</v>
@@ -6372,19 +6372,19 @@
         <v>0.132</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.316</v>
+        <v>0.342</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.417</v>
+        <v>0.385</v>
       </c>
       <c r="AK38" t="n">
         <v>0.6840000000000001</v>
       </c>
       <c r="AL38" t="n">
-        <v>2.184</v>
+        <v>2.158</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.313</v>
+        <v>0.317</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
@@ -6507,13 +6507,13 @@
         <v>0.222</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.583</v>
+        <v>1.778</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.333</v>
+        <v>2.528</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.775</v>
+        <v>0.703</v>
       </c>
       <c r="AB39" t="n">
         <v>0.278</v>
@@ -6672,13 +6672,13 @@
         <v>0.579</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.026</v>
+        <v>1.026</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.684</v>
+        <v>1.684</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.755</v>
+        <v>0.609</v>
       </c>
       <c r="AB40" t="n">
         <v>0.763</v>
@@ -6837,10 +6837,10 @@
         <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="AA41" t="n">
         <v>1</v>
@@ -7002,13 +7002,13 @@
         <v>0.735</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.647</v>
+        <v>0.853</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.971</v>
+        <v>1.176</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.836</v>
+        <v>0.725</v>
       </c>
       <c r="AB42" t="n">
         <v>0.147</v>
@@ -7032,19 +7032,19 @@
         <v>0.235</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.5</v>
+        <v>0.529</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.471</v>
+        <v>0.444</v>
       </c>
       <c r="AK42" t="n">
         <v>0.971</v>
       </c>
       <c r="AL42" t="n">
-        <v>2.5</v>
+        <v>2.471</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.388</v>
+        <v>0.393</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
@@ -7332,13 +7332,13 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.111</v>
+        <v>0.667</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.222</v>
+        <v>0.778</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.909</v>
+        <v>0.857</v>
       </c>
       <c r="AB44" t="n">
         <v>0</v>
@@ -7527,19 +7527,19 @@
         <v>0.333</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AK45" t="n">
         <v>0.333</v>
       </c>
       <c r="AL45" t="n">
-        <v>2.667</v>
+        <v>2.333</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.125</v>
+        <v>0.143</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
@@ -7827,13 +7827,13 @@
         <v>6.895</v>
       </c>
       <c r="Y47" t="n">
-        <v>28.737</v>
+        <v>14.737</v>
       </c>
       <c r="Z47" t="n">
-        <v>35.474</v>
+        <v>21.474</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="AB47" t="n">
         <v>5.184</v>
@@ -7854,22 +7854,22 @@
         <v>0.418</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.711</v>
+        <v>1.763</v>
       </c>
       <c r="AI47" t="n">
-        <v>4.447</v>
+        <v>4.737</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.385</v>
+        <v>0.372</v>
       </c>
       <c r="AK47" t="n">
-        <v>9.974</v>
+        <v>9.920999999999999</v>
       </c>
       <c r="AL47" t="n">
-        <v>27.395</v>
+        <v>27.105</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.364</v>
+        <v>0.366</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
@@ -7992,13 +7992,13 @@
         <v>5.868</v>
       </c>
       <c r="Y48" t="n">
-        <v>29.684</v>
+        <v>13.763</v>
       </c>
       <c r="Z48" t="n">
-        <v>37.105</v>
+        <v>21.184</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.8</v>
+        <v>0.65</v>
       </c>
       <c r="AB48" t="n">
         <v>6.079</v>
@@ -8019,22 +8019,22 @@
         <v>0.462</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.289</v>
+        <v>1.5</v>
       </c>
       <c r="AI48" t="n">
-        <v>3.421</v>
+        <v>3.895</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.377</v>
+        <v>0.385</v>
       </c>
       <c r="AK48" t="n">
-        <v>8.211</v>
+        <v>8</v>
       </c>
       <c r="AL48" t="n">
-        <v>23.921</v>
+        <v>23.447</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.343</v>
+        <v>0.341</v>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
